--- a/example/i18n/langs/en/equip.xlsx
+++ b/example/i18n/langs/en/equip.xlsx
@@ -13,7 +13,7 @@
     <workbookView xWindow="0" yWindow="10410" windowWidth="38400" windowHeight="10470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="equip.jewelrysuit" sheetId="1" r:id="rId1"/>
+    <sheet name="equip.jewelry_suit" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
